--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:22</t>
+    <t xml:space="preserve">2026-09-10 01:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:37</t>
+    <t xml:space="preserve">2026-09-18 11:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:33</t>
+    <t xml:space="preserve">2026-09-23 15:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:38</t>
+    <t xml:space="preserve">2026-10-05 16:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -826,7 +826,7 @@
         <v>45.52</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>55.74</v>
+        <v>55.75</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>100.61</v>
